--- a/data/trans_orig/P36BPD10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023</t>
+          <t>Población según el número de raciones pescado o mariscos que consumen a la semana en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21791</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44138</t>
+          <t>43481</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27650</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47496</t>
+          <t>47694</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53796</t>
+          <t>53449</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82128</t>
+          <t>84654</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>246599</t>
+          <t>249368</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>301173</t>
+          <t>302607</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>275124</t>
+          <t>273849</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>315007</t>
+          <t>314835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>46,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>531850</t>
+          <t>534572</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>600269</t>
+          <t>601266</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,69%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>46,0%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>299194</t>
+          <t>296393</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>355457</t>
+          <t>353310</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,89%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>324487</t>
+          <t>325620</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>362970</t>
+          <t>366383</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,08%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>641700</t>
+          <t>637740</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>709898</t>
+          <t>705821</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,0%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45139</t>
+          <t>45918</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>119114</t>
+          <t>121371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53901</t>
+          <t>53732</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>82713</t>
+          <t>79807</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>98475</t>
+          <t>107845</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>185387</t>
+          <t>190768</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>591945</t>
+          <t>594545</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>942548</t>
+          <t>973522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>443101</t>
+          <t>443764</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>496665</t>
+          <t>497259</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1060100</t>
+          <t>1058158</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1495991</t>
+          <t>1524993</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>202634</t>
+          <t>188451</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>494820</t>
+          <t>493370</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,5%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>394641</t>
+          <t>393444</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>447822</t>
+          <t>446105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>549802</t>
+          <t>506471</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>920039</t>
+          <t>915969</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,8%</t>
+          <t>42,61%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>96177</t>
+          <t>93749</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>143277</t>
+          <t>144827</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52836</t>
+          <t>46651</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>135125</t>
+          <t>139081</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1692,12 +1692,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>138952</t>
+          <t>142475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>261013</t>
+          <t>259752</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,86%</t>
         </is>
       </c>
     </row>
@@ -1755,12 +1755,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>264475</t>
+          <t>266872</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>328403</t>
+          <t>329434</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1770,12 +1770,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>160694</t>
+          <t>151355</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>394973</t>
+          <t>392614</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1805,12 +1805,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>403659</t>
+          <t>405859</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>694962</t>
+          <t>697453</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1840,12 +1840,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,58%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>260382</t>
+          <t>263288</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324635</t>
+          <t>324436</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>412163</t>
+          <t>408449</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>724711</t>
+          <t>736498</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>695756</t>
+          <t>696368</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1097144</t>
+          <t>1092661</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>66,71%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>77079</t>
+          <t>73839</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>124162</t>
+          <t>118891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,47 +2113,47 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>7,98%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>12,85%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>91127</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>71653</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>108219</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
           <t>8,33%</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>91127</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>69235</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>108851</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>8,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>157630</t>
+          <t>158927</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>217632</t>
+          <t>221307</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,96%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405563</t>
+          <t>405303</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>472120</t>
+          <t>469075</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,03%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473294</t>
+          <t>473042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>639351</t>
+          <t>626052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>904915</t>
+          <t>901415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1099922</t>
+          <t>1088742</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,91%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>361240</t>
+          <t>359466</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>425402</t>
+          <t>425947</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>46,04%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>382468</t>
+          <t>392261</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>525044</t>
+          <t>525779</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>34,95%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>48,05%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>765551</t>
+          <t>769143</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>924712</t>
+          <t>925604</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>255736</t>
+          <t>264001</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>381948</t>
+          <t>383751</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239610</t>
+          <t>235356</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>328744</t>
+          <t>329673</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>530840</t>
+          <t>536943</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>691546</t>
+          <t>695730</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,78%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1578156</t>
+          <t>1579914</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2107175</t>
+          <t>2170613</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1297094</t>
+          <t>1311584</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1714346</t>
+          <t>1720948</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2717,12 +2717,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,44%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3060550</t>
+          <t>3022582</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3689488</t>
+          <t>3725865</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>52,37%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1077680</t>
+          <t>1060345</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1518127</t>
+          <t>1516187</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1645345</t>
+          <t>1638491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2136723</t>
+          <t>2096734</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2892755</t>
+          <t>2869289</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3495261</t>
+          <t>3526907</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36BPD10_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P36BPD10_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>31063</t>
+          <t>37177</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21915</t>
+          <t>27761</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43481</t>
+          <t>51638</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35792</t>
+          <t>41458</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27713</t>
+          <t>32494</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>47694</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66855</t>
+          <t>78635</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53449</t>
+          <t>63934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84654</t>
+          <t>96871</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>273772</t>
+          <t>294627</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>249368</t>
+          <t>267026</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>302607</t>
+          <t>320773</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>46,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>294837</t>
+          <t>319829</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>273849</t>
+          <t>299773</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>314835</t>
+          <t>344324</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,65%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,27 +908,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>568609</t>
+          <t>614456</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>534572</t>
+          <t>578345</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>601266</t>
+          <t>653018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>327257</t>
+          <t>355379</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>296393</t>
+          <t>326100</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>353310</t>
+          <t>382039</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>51,77%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>47,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>344330</t>
+          <t>371019</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>325620</t>
+          <t>347602</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>366383</t>
+          <t>393059</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>671588</t>
+          <t>726399</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>637740</t>
+          <t>688379</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>705821</t>
+          <t>762070</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>51,38%</t>
+          <t>51,17%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>632092</t>
+          <t>687183</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>632092</t>
+          <t>687183</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>632092</t>
+          <t>687183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>674959</t>
+          <t>732306</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>674959</t>
+          <t>732306</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>674959</t>
+          <t>732306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>1307051</t>
+          <t>1419489</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1307051</t>
+          <t>1419489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1307051</t>
+          <t>1419489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>84776</t>
+          <t>85253</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45918</t>
+          <t>68959</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121371</t>
+          <t>109131</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>66721</t>
+          <t>78900</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>53732</t>
+          <t>64933</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>79807</t>
+          <t>94120</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>151498</t>
+          <t>164153</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>107845</t>
+          <t>140793</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>190768</t>
+          <t>191097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,02%</t>
         </is>
       </c>
     </row>
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>727380</t>
+          <t>552453</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>594545</t>
+          <t>515743</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>973522</t>
+          <t>590857</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49,87%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>56,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,67 +1329,67 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>470130</t>
+          <t>532065</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>443764</t>
+          <t>501296</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>497259</t>
+          <t>557507</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
+          <t>49,72%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>52,1%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1221</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1084518</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1040068</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>1130099</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
           <t>49,1%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>46,35%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>51,94%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1221</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1197510</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>1058158</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1524993</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>55,71%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>49,22%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>53,35%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>380111</t>
+          <t>410511</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>188451</t>
+          <t>374713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>493370</t>
+          <t>445701</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>420590</t>
+          <t>459117</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>393444</t>
+          <t>433420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>446105</t>
+          <t>490533</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>42,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,59%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>800701</t>
+          <t>869627</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>506471</t>
+          <t>823957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>915969</t>
+          <t>913271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,11%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1192267</t>
+          <t>1048217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1192267</t>
+          <t>1048217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1192267</t>
+          <t>1048217</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>957441</t>
+          <t>1070081</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>957441</t>
+          <t>1070081</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>957441</t>
+          <t>1070081</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>2149708</t>
+          <t>2118298</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2149708</t>
+          <t>2118298</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>2149708</t>
+          <t>2118298</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>116850</t>
+          <t>129756</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93749</t>
+          <t>108702</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>144827</t>
+          <t>156063</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,32 +1672,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>98557</t>
+          <t>115644</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46651</t>
+          <t>97839</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>139081</t>
+          <t>137220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>215406</t>
+          <t>245400</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>142475</t>
+          <t>213666</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>259752</t>
+          <t>278214</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,22%</t>
         </is>
       </c>
     </row>
@@ -1750,32 +1750,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>297161</t>
+          <t>345946</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>266872</t>
+          <t>313764</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>329434</t>
+          <t>380309</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,32 +1785,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>295979</t>
+          <t>340913</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>151355</t>
+          <t>314232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>392614</t>
+          <t>365962</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,06%</t>
+          <t>45,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,32 +1820,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>593140</t>
+          <t>686858</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>405859</t>
+          <t>644579</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>697453</t>
+          <t>728089</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>42,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>45,07%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>290669</t>
+          <t>327372</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>263288</t>
+          <t>297659</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>324436</t>
+          <t>362727</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>538830</t>
+          <t>355702</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>408449</t>
+          <t>331421</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>736498</t>
+          <t>384438</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>829499</t>
+          <t>683073</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>696368</t>
+          <t>641753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1092661</t>
+          <t>721562</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>95925</t>
+          <t>102452</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73839</t>
+          <t>82398</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118891</t>
+          <t>127435</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>91127</t>
+          <t>102116</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71653</t>
+          <t>85786</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>108219</t>
+          <t>120469</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>187052</t>
+          <t>204568</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>158927</t>
+          <t>178114</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>221307</t>
+          <t>234802</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>438194</t>
+          <t>471411</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>405303</t>
+          <t>438175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>469075</t>
+          <t>502183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>521921</t>
+          <t>505162</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473042</t>
+          <t>474818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>626052</t>
+          <t>535564</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>47,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>960115</t>
+          <t>976573</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>901415</t>
+          <t>933247</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1088742</t>
+          <t>1023389</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>47,54%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>48,57%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>391046</t>
+          <t>414706</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>359466</t>
+          <t>381993</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>425947</t>
+          <t>447139</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>41,95%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,85%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>481242</t>
+          <t>511072</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>392261</t>
+          <t>482367</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>525779</t>
+          <t>540228</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>45,7%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>48,05%</t>
+          <t>48,31%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>872289</t>
+          <t>925779</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>769143</t>
+          <t>883377</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>925604</t>
+          <t>971708</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,94%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>46,12%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>925166</t>
+          <t>988569</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>925166</t>
+          <t>988569</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>925166</t>
+          <t>988569</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1094290</t>
+          <t>1118351</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1094290</t>
+          <t>1118351</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1094290</t>
+          <t>1118351</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>2019456</t>
+          <t>2106920</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2019456</t>
+          <t>2106920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>2019456</t>
+          <t>2106920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>328614</t>
+          <t>354638</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>264001</t>
+          <t>314782</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>383751</t>
+          <t>398559</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>292197</t>
+          <t>338119</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235356</t>
+          <t>307751</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>329673</t>
+          <t>371825</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>620811</t>
+          <t>692756</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>536943</t>
+          <t>639373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>695730</t>
+          <t>748690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1736507</t>
+          <t>1664437</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1579914</t>
+          <t>1601546</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2170613</t>
+          <t>1729154</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>47,19%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>49,03%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,32 +2697,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1582867</t>
+          <t>1697968</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1311584</t>
+          <t>1647252</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1720948</t>
+          <t>1756622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>47,02%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3319374</t>
+          <t>3362404</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>3022582</t>
+          <t>3275951</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>3725865</t>
+          <t>3450220</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1389084</t>
+          <t>1507968</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1060345</t>
+          <t>1440062</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1516187</t>
+          <t>1570302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1784993</t>
+          <t>1696910</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1638491</t>
+          <t>1644444</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2096734</t>
+          <t>1748824</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>46,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3174077</t>
+          <t>3204877</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2869289</t>
+          <t>3112574</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>3526907</t>
+          <t>3284075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>45,23%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3454205</t>
+          <t>3527042</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3660057</t>
+          <t>3732996</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7114262</t>
+          <t>7260038</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
